--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 07:07 UTC</t>
+    <t>2026-10-10 07:12 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 07:12 UTC</t>
+    <t>2026-10-10 09:11 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 09:11 UTC</t>
+    <t>2026-10-10 09:14 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -28,7 +28,7 @@
     <t>Verified V1 features</t>
   </si>
   <si>
-    <t>0 / 144</t>
+    <t>0 / 140</t>
   </si>
   <si>
     <t>V1 feature progress</t>
@@ -382,6 +382,9 @@
     <t>FIN-027</t>
   </si>
   <si>
+    <t>V1.5</t>
+  </si>
+  <si>
     <t>Supported bank PDF parser #2</t>
   </si>
   <si>
@@ -1469,9 +1472,6 @@
   </si>
   <si>
     <t>FIN-145</t>
-  </si>
-  <si>
-    <t>V1.5</t>
   </si>
   <si>
     <t>Expanded personal finance</t>
@@ -4134,20 +4134,18 @@
         <v>121</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="8">
-        <v>14</v>
-      </c>
+      <c r="G31" s="8"/>
       <c r="H31" s="8" t="s">
         <v>32</v>
       </c>
@@ -4166,7 +4164,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>28</v>
@@ -4175,7 +4173,7 @@
         <v>91</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>31</v>
@@ -4187,7 +4185,7 @@
         <v>32</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>34</v>
@@ -4201,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>28</v>
@@ -4210,7 +4208,7 @@
         <v>91</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -4222,7 +4220,7 @@
         <v>32</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>34</v>
@@ -4236,7 +4234,7 @@
         <v>26</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>28</v>
@@ -4245,7 +4243,7 @@
         <v>91</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>31</v>
@@ -4257,7 +4255,7 @@
         <v>32</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>34</v>
@@ -4271,7 +4269,7 @@
         <v>26</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>28</v>
@@ -4280,7 +4278,7 @@
         <v>91</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>31</v>
@@ -4292,7 +4290,7 @@
         <v>32</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>34</v>
@@ -4306,7 +4304,7 @@
         <v>26</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>28</v>
@@ -4315,7 +4313,7 @@
         <v>91</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>31</v>
@@ -4327,7 +4325,7 @@
         <v>32</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>34</v>
@@ -4341,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>28</v>
@@ -4350,7 +4348,7 @@
         <v>91</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4360,7 @@
         <v>32</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>34</v>
@@ -4376,7 +4374,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>28</v>
@@ -4385,7 +4383,7 @@
         <v>91</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>31</v>
@@ -4397,7 +4395,7 @@
         <v>32</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>34</v>
@@ -4411,16 +4409,16 @@
         <v>26</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>31</v>
@@ -4432,7 +4430,7 @@
         <v>32</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>34</v>
@@ -4446,16 +4444,16 @@
         <v>26</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>31</v>
@@ -4467,7 +4465,7 @@
         <v>32</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>34</v>
@@ -4481,16 +4479,16 @@
         <v>26</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -4502,7 +4500,7 @@
         <v>32</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>34</v>
@@ -4516,16 +4514,16 @@
         <v>26</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>31</v>
@@ -4537,7 +4535,7 @@
         <v>32</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>34</v>
@@ -4551,16 +4549,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>31</v>
@@ -4572,7 +4570,7 @@
         <v>32</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
@@ -4586,16 +4584,16 @@
         <v>26</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>31</v>
@@ -4607,7 +4605,7 @@
         <v>32</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>34</v>
@@ -4621,16 +4619,16 @@
         <v>26</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -4642,7 +4640,7 @@
         <v>32</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>34</v>
@@ -4656,16 +4654,16 @@
         <v>26</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>31</v>
@@ -4677,7 +4675,7 @@
         <v>32</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>34</v>
@@ -4691,16 +4689,16 @@
         <v>26</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>31</v>
@@ -4712,7 +4710,7 @@
         <v>32</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>34</v>
@@ -4726,16 +4724,16 @@
         <v>26</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>31</v>
@@ -4747,7 +4745,7 @@
         <v>32</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>34</v>
@@ -4761,16 +4759,16 @@
         <v>26</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -4782,7 +4780,7 @@
         <v>32</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>34</v>
@@ -4796,16 +4794,16 @@
         <v>26</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>31</v>
@@ -4817,7 +4815,7 @@
         <v>32</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>34</v>
@@ -4831,16 +4829,16 @@
         <v>26</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>31</v>
@@ -4852,7 +4850,7 @@
         <v>32</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>34</v>
@@ -4866,16 +4864,16 @@
         <v>26</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>31</v>
@@ -4887,7 +4885,7 @@
         <v>32</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>34</v>
@@ -4901,16 +4899,16 @@
         <v>26</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -4922,7 +4920,7 @@
         <v>32</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>34</v>
@@ -4936,16 +4934,16 @@
         <v>26</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>31</v>
@@ -4957,7 +4955,7 @@
         <v>32</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>34</v>
@@ -4971,16 +4969,16 @@
         <v>26</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>31</v>
@@ -4992,7 +4990,7 @@
         <v>32</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>34</v>
@@ -5006,16 +5004,16 @@
         <v>26</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>31</v>
@@ -5027,7 +5025,7 @@
         <v>32</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>34</v>
@@ -5041,16 +5039,16 @@
         <v>26</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -5062,7 +5060,7 @@
         <v>32</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>34</v>
@@ -5076,16 +5074,16 @@
         <v>26</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>31</v>
@@ -5097,7 +5095,7 @@
         <v>32</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>34</v>
@@ -5111,16 +5109,16 @@
         <v>26</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>31</v>
@@ -5132,7 +5130,7 @@
         <v>32</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>34</v>
@@ -5146,16 +5144,16 @@
         <v>26</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>31</v>
@@ -5167,7 +5165,7 @@
         <v>32</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>34</v>
@@ -5181,16 +5179,16 @@
         <v>26</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -5202,7 +5200,7 @@
         <v>32</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>34</v>
@@ -5216,16 +5214,16 @@
         <v>26</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>31</v>
@@ -5237,7 +5235,7 @@
         <v>32</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>34</v>
@@ -5251,16 +5249,16 @@
         <v>26</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -5272,7 +5270,7 @@
         <v>32</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>34</v>
@@ -5286,16 +5284,16 @@
         <v>26</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>31</v>
@@ -5307,7 +5305,7 @@
         <v>32</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>34</v>
@@ -5321,16 +5319,16 @@
         <v>26</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>31</v>
@@ -5342,7 +5340,7 @@
         <v>32</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>34</v>
@@ -5356,16 +5354,16 @@
         <v>26</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>31</v>
@@ -5377,7 +5375,7 @@
         <v>32</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>34</v>
@@ -5391,28 +5389,26 @@
         <v>26</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="8">
-        <v>39</v>
-      </c>
+      <c r="G67" s="8"/>
       <c r="H67" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>34</v>
@@ -5426,16 +5422,16 @@
         <v>26</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>31</v>
@@ -5447,7 +5443,7 @@
         <v>32</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>34</v>
@@ -5461,16 +5457,16 @@
         <v>26</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>31</v>
@@ -5482,7 +5478,7 @@
         <v>32</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J69" s="8" t="s">
         <v>34</v>
@@ -5496,28 +5492,26 @@
         <v>26</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G70" s="11">
-        <v>39</v>
-      </c>
+      <c r="G70" s="8"/>
       <c r="H70" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>34</v>
@@ -5531,28 +5525,26 @@
         <v>26</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G71" s="8">
-        <v>39</v>
-      </c>
+      <c r="G71" s="8"/>
       <c r="H71" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J71" s="8" t="s">
         <v>34</v>
@@ -5566,16 +5558,16 @@
         <v>26</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>31</v>
@@ -5587,7 +5579,7 @@
         <v>32</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>34</v>
@@ -5601,16 +5593,16 @@
         <v>26</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>31</v>
@@ -5622,7 +5614,7 @@
         <v>32</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>34</v>
@@ -5636,16 +5628,16 @@
         <v>26</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>31</v>
@@ -5657,7 +5649,7 @@
         <v>32</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>34</v>
@@ -5671,16 +5663,16 @@
         <v>26</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -5692,7 +5684,7 @@
         <v>32</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>34</v>
@@ -5706,16 +5698,16 @@
         <v>26</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>31</v>
@@ -5727,7 +5719,7 @@
         <v>32</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>34</v>
@@ -5741,16 +5733,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>31</v>
@@ -5762,7 +5754,7 @@
         <v>32</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>34</v>
@@ -5776,16 +5768,16 @@
         <v>26</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>31</v>
@@ -5797,7 +5789,7 @@
         <v>32</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>34</v>
@@ -5811,16 +5803,16 @@
         <v>26</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -5832,7 +5824,7 @@
         <v>32</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>34</v>
@@ -5846,16 +5838,16 @@
         <v>26</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>31</v>
@@ -5867,7 +5859,7 @@
         <v>32</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>34</v>
@@ -5881,16 +5873,16 @@
         <v>26</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>31</v>
@@ -5902,7 +5894,7 @@
         <v>32</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>34</v>
@@ -5916,16 +5908,16 @@
         <v>26</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>31</v>
@@ -5937,7 +5929,7 @@
         <v>32</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>34</v>
@@ -5951,16 +5943,16 @@
         <v>26</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -5972,7 +5964,7 @@
         <v>32</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>34</v>
@@ -5986,16 +5978,16 @@
         <v>26</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>31</v>
@@ -6007,7 +5999,7 @@
         <v>32</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>34</v>
@@ -6021,16 +6013,16 @@
         <v>26</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>31</v>
@@ -6042,7 +6034,7 @@
         <v>32</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>34</v>
@@ -6056,16 +6048,16 @@
         <v>26</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>31</v>
@@ -6077,7 +6069,7 @@
         <v>32</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>34</v>
@@ -6091,16 +6083,16 @@
         <v>26</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -6112,7 +6104,7 @@
         <v>32</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>34</v>
@@ -6126,16 +6118,16 @@
         <v>26</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>31</v>
@@ -6147,7 +6139,7 @@
         <v>32</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>34</v>
@@ -6161,16 +6153,16 @@
         <v>26</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>31</v>
@@ -6182,7 +6174,7 @@
         <v>32</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>34</v>
@@ -6196,16 +6188,16 @@
         <v>26</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>31</v>
@@ -6217,7 +6209,7 @@
         <v>32</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>34</v>
@@ -6231,16 +6223,16 @@
         <v>26</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -6252,7 +6244,7 @@
         <v>32</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>34</v>
@@ -6266,16 +6258,16 @@
         <v>26</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>31</v>
@@ -6287,7 +6279,7 @@
         <v>32</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>34</v>
@@ -6301,16 +6293,16 @@
         <v>26</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -6322,7 +6314,7 @@
         <v>32</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>34</v>
@@ -6336,16 +6328,16 @@
         <v>26</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>31</v>
@@ -6357,7 +6349,7 @@
         <v>32</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>34</v>
@@ -6371,16 +6363,16 @@
         <v>26</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>31</v>
@@ -6392,7 +6384,7 @@
         <v>32</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>34</v>
@@ -6406,16 +6398,16 @@
         <v>26</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>31</v>
@@ -6427,7 +6419,7 @@
         <v>32</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>34</v>
@@ -6441,16 +6433,16 @@
         <v>26</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -6462,7 +6454,7 @@
         <v>32</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>34</v>
@@ -6476,16 +6468,16 @@
         <v>26</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>31</v>
@@ -6497,7 +6489,7 @@
         <v>32</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>34</v>
@@ -6511,16 +6503,16 @@
         <v>26</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>31</v>
@@ -6532,7 +6524,7 @@
         <v>32</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>34</v>
@@ -6546,16 +6538,16 @@
         <v>26</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>31</v>
@@ -6567,7 +6559,7 @@
         <v>32</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>34</v>
@@ -6581,16 +6573,16 @@
         <v>26</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -6602,7 +6594,7 @@
         <v>32</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>34</v>
@@ -6616,16 +6608,16 @@
         <v>26</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>31</v>
@@ -6637,7 +6629,7 @@
         <v>32</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>34</v>
@@ -6651,16 +6643,16 @@
         <v>26</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>31</v>
@@ -6672,7 +6664,7 @@
         <v>32</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>34</v>
@@ -6686,16 +6678,16 @@
         <v>26</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>31</v>
@@ -6707,7 +6699,7 @@
         <v>32</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>34</v>
@@ -6721,16 +6713,16 @@
         <v>26</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -6742,7 +6734,7 @@
         <v>32</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>34</v>
@@ -6756,16 +6748,16 @@
         <v>26</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>31</v>
@@ -6777,7 +6769,7 @@
         <v>32</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>34</v>
@@ -6791,16 +6783,16 @@
         <v>26</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>31</v>
@@ -6812,7 +6804,7 @@
         <v>32</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>34</v>
@@ -6826,16 +6818,16 @@
         <v>26</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>31</v>
@@ -6847,7 +6839,7 @@
         <v>32</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>34</v>
@@ -6861,16 +6853,16 @@
         <v>26</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -6882,7 +6874,7 @@
         <v>32</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J109" s="8" t="s">
         <v>34</v>
@@ -6896,16 +6888,16 @@
         <v>26</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>31</v>
@@ -6917,7 +6909,7 @@
         <v>32</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>34</v>
@@ -6931,16 +6923,16 @@
         <v>26</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>31</v>
@@ -6952,7 +6944,7 @@
         <v>32</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J111" s="8" t="s">
         <v>34</v>
@@ -6966,19 +6958,19 @@
         <v>26</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G112" s="11">
         <v>69</v>
@@ -6987,7 +6979,7 @@
         <v>32</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>34</v>
@@ -7001,19 +6993,19 @@
         <v>26</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G113" s="8">
         <v>69</v>
@@ -7022,7 +7014,7 @@
         <v>32</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>34</v>
@@ -7036,19 +7028,19 @@
         <v>26</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G114" s="11">
         <v>69</v>
@@ -7057,7 +7049,7 @@
         <v>32</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>34</v>
@@ -7071,19 +7063,19 @@
         <v>26</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G115" s="8">
         <v>69</v>
@@ -7092,7 +7084,7 @@
         <v>32</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>34</v>
@@ -7106,19 +7098,19 @@
         <v>26</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G116" s="11">
         <v>69</v>
@@ -7127,7 +7119,7 @@
         <v>32</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>34</v>
@@ -7141,19 +7133,19 @@
         <v>26</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G117" s="8">
         <v>69</v>
@@ -7162,7 +7154,7 @@
         <v>32</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>34</v>
@@ -7176,19 +7168,19 @@
         <v>26</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G118" s="11">
         <v>69</v>
@@ -7197,7 +7189,7 @@
         <v>32</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>34</v>
@@ -7211,19 +7203,19 @@
         <v>26</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G119" s="8">
         <v>69</v>
@@ -7232,7 +7224,7 @@
         <v>32</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>34</v>
@@ -7246,19 +7238,19 @@
         <v>26</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C120" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G120" s="11">
         <v>69</v>
@@ -7267,7 +7259,7 @@
         <v>32</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>34</v>
@@ -7281,19 +7273,19 @@
         <v>26</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G121" s="8">
         <v>69</v>
@@ -7302,7 +7294,7 @@
         <v>32</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>34</v>
@@ -7316,19 +7308,19 @@
         <v>26</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G122" s="11">
         <v>69</v>
@@ -7337,7 +7329,7 @@
         <v>32</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>34</v>
@@ -7351,19 +7343,19 @@
         <v>26</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G123" s="8">
         <v>69</v>
@@ -7372,7 +7364,7 @@
         <v>32</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J123" s="8" t="s">
         <v>34</v>
@@ -7386,19 +7378,19 @@
         <v>26</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G124" s="11">
         <v>69</v>
@@ -7407,7 +7399,7 @@
         <v>32</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>34</v>
@@ -7421,19 +7413,19 @@
         <v>26</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G125" s="8">
         <v>69</v>
@@ -7442,7 +7434,7 @@
         <v>32</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J125" s="8" t="s">
         <v>34</v>
@@ -7456,19 +7448,19 @@
         <v>26</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G126" s="11">
         <v>69</v>
@@ -7477,7 +7469,7 @@
         <v>32</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>34</v>
@@ -7491,19 +7483,19 @@
         <v>26</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G127" s="8">
         <v>69</v>
@@ -7512,7 +7504,7 @@
         <v>32</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>34</v>
@@ -7526,19 +7518,19 @@
         <v>26</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G128" s="11">
         <v>69</v>
@@ -7547,7 +7539,7 @@
         <v>32</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>34</v>
@@ -7561,19 +7553,19 @@
         <v>26</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G129" s="8">
         <v>69</v>
@@ -7582,7 +7574,7 @@
         <v>32</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J129" s="8" t="s">
         <v>34</v>
@@ -7596,19 +7588,19 @@
         <v>26</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G130" s="11">
         <v>69</v>
@@ -7617,7 +7609,7 @@
         <v>32</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>34</v>
@@ -7631,19 +7623,19 @@
         <v>26</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G131" s="8">
         <v>74</v>
@@ -7652,7 +7644,7 @@
         <v>32</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J131" s="8" t="s">
         <v>34</v>
@@ -7666,19 +7658,19 @@
         <v>26</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G132" s="11">
         <v>74</v>
@@ -7687,7 +7679,7 @@
         <v>32</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>34</v>
@@ -7701,19 +7693,19 @@
         <v>26</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G133" s="8">
         <v>74</v>
@@ -7722,7 +7714,7 @@
         <v>32</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J133" s="8" t="s">
         <v>34</v>
@@ -7736,19 +7728,19 @@
         <v>26</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G134" s="11">
         <v>74</v>
@@ -7757,7 +7749,7 @@
         <v>32</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>34</v>
@@ -7771,19 +7763,19 @@
         <v>26</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G135" s="8">
         <v>74</v>
@@ -7792,7 +7784,7 @@
         <v>32</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J135" s="8" t="s">
         <v>34</v>
@@ -7806,19 +7798,19 @@
         <v>26</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G136" s="11">
         <v>74</v>
@@ -7827,7 +7819,7 @@
         <v>32</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>34</v>
@@ -7841,19 +7833,19 @@
         <v>26</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G137" s="8">
         <v>74</v>
@@ -7862,7 +7854,7 @@
         <v>32</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J137" s="8" t="s">
         <v>34</v>
@@ -7876,19 +7868,19 @@
         <v>26</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G138" s="11">
         <v>74</v>
@@ -7897,7 +7889,7 @@
         <v>32</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>34</v>
@@ -7911,19 +7903,19 @@
         <v>26</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G139" s="8">
         <v>74</v>
@@ -7932,7 +7924,7 @@
         <v>32</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J139" s="8" t="s">
         <v>34</v>
@@ -7946,19 +7938,19 @@
         <v>26</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G140" s="11">
         <v>74</v>
@@ -7967,7 +7959,7 @@
         <v>32</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>34</v>
@@ -7981,19 +7973,19 @@
         <v>26</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G141" s="8">
         <v>74</v>
@@ -8002,7 +7994,7 @@
         <v>32</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J141" s="8" t="s">
         <v>34</v>
@@ -8016,19 +8008,19 @@
         <v>26</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G142" s="11">
         <v>74</v>
@@ -8037,7 +8029,7 @@
         <v>32</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>34</v>
@@ -8051,19 +8043,19 @@
         <v>26</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G143" s="8">
         <v>74</v>
@@ -8072,7 +8064,7 @@
         <v>32</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J143" s="8" t="s">
         <v>34</v>
@@ -8086,19 +8078,19 @@
         <v>26</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G144" s="11">
         <v>74</v>
@@ -8107,7 +8099,7 @@
         <v>32</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>34</v>
@@ -8121,19 +8113,19 @@
         <v>26</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G145" s="8">
         <v>74</v>
@@ -8142,7 +8134,7 @@
         <v>32</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J145" s="8" t="s">
         <v>34</v>
@@ -8156,19 +8148,19 @@
         <v>26</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G146" s="11">
         <v>74</v>
@@ -8177,7 +8169,7 @@
         <v>32</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>34</v>
@@ -8191,19 +8183,19 @@
         <v>26</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G147" s="8">
         <v>74</v>
@@ -8212,7 +8204,7 @@
         <v>32</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J147" s="8" t="s">
         <v>34</v>
@@ -8226,19 +8218,19 @@
         <v>26</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G148" s="11">
         <v>74</v>
@@ -8247,7 +8239,7 @@
         <v>32</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>34</v>
@@ -8261,10 +8253,10 @@
         <v>26</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>486</v>
@@ -8297,7 +8289,7 @@
         <v>490</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D150" s="11" t="s">
         <v>486</v>
@@ -8330,7 +8322,7 @@
         <v>493</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>486</v>
@@ -8363,7 +8355,7 @@
         <v>496</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D152" s="11" t="s">
         <v>486</v>
@@ -8396,7 +8388,7 @@
         <v>499</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>486</v>
@@ -8429,7 +8421,7 @@
         <v>502</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D154" s="11" t="s">
         <v>486</v>
@@ -8462,7 +8454,7 @@
         <v>505</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>486</v>
@@ -8495,7 +8487,7 @@
         <v>508</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D156" s="11" t="s">
         <v>486</v>
@@ -8528,7 +8520,7 @@
         <v>511</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>486</v>
@@ -8561,7 +8553,7 @@
         <v>514</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D158" s="11" t="s">
         <v>486</v>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -28,7 +28,7 @@
     <t>Verified V1 features</t>
   </si>
   <si>
-    <t>0 / 144</t>
+    <t>0 / 140</t>
   </si>
   <si>
     <t>V1 feature progress</t>
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 09:14 UTC</t>
+    <t>2026-10-10 09:55 UTC</t>
   </si>
   <si>
     <t>Source</t>
@@ -382,6 +382,9 @@
     <t>FIN-027</t>
   </si>
   <si>
+    <t>V1.5</t>
+  </si>
+  <si>
     <t>Supported bank PDF parser #2</t>
   </si>
   <si>
@@ -1469,9 +1472,6 @@
   </si>
   <si>
     <t>FIN-145</t>
-  </si>
-  <si>
-    <t>V1.5</t>
   </si>
   <si>
     <t>Expanded personal finance</t>
@@ -4134,20 +4134,18 @@
         <v>121</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="8">
-        <v>14</v>
-      </c>
+      <c r="G31" s="8"/>
       <c r="H31" s="8" t="s">
         <v>32</v>
       </c>
@@ -4166,7 +4164,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>28</v>
@@ -4175,7 +4173,7 @@
         <v>91</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>31</v>
@@ -4187,7 +4185,7 @@
         <v>32</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>34</v>
@@ -4201,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>28</v>
@@ -4210,7 +4208,7 @@
         <v>91</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -4222,7 +4220,7 @@
         <v>32</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>34</v>
@@ -4236,7 +4234,7 @@
         <v>26</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>28</v>
@@ -4245,7 +4243,7 @@
         <v>91</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>31</v>
@@ -4257,7 +4255,7 @@
         <v>32</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>34</v>
@@ -4271,7 +4269,7 @@
         <v>26</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>28</v>
@@ -4280,7 +4278,7 @@
         <v>91</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>31</v>
@@ -4292,7 +4290,7 @@
         <v>32</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>34</v>
@@ -4306,7 +4304,7 @@
         <v>26</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>28</v>
@@ -4315,7 +4313,7 @@
         <v>91</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>31</v>
@@ -4327,7 +4325,7 @@
         <v>32</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>34</v>
@@ -4341,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>28</v>
@@ -4350,7 +4348,7 @@
         <v>91</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -4362,7 +4360,7 @@
         <v>32</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>34</v>
@@ -4376,7 +4374,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>28</v>
@@ -4385,7 +4383,7 @@
         <v>91</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>31</v>
@@ -4397,7 +4395,7 @@
         <v>32</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>34</v>
@@ -4411,16 +4409,16 @@
         <v>26</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>31</v>
@@ -4432,7 +4430,7 @@
         <v>32</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>34</v>
@@ -4446,16 +4444,16 @@
         <v>26</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>31</v>
@@ -4467,7 +4465,7 @@
         <v>32</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>34</v>
@@ -4481,16 +4479,16 @@
         <v>26</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -4502,7 +4500,7 @@
         <v>32</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>34</v>
@@ -4516,16 +4514,16 @@
         <v>26</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>31</v>
@@ -4537,7 +4535,7 @@
         <v>32</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>34</v>
@@ -4551,16 +4549,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>31</v>
@@ -4572,7 +4570,7 @@
         <v>32</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
@@ -4586,16 +4584,16 @@
         <v>26</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>31</v>
@@ -4607,7 +4605,7 @@
         <v>32</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>34</v>
@@ -4621,16 +4619,16 @@
         <v>26</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -4642,7 +4640,7 @@
         <v>32</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>34</v>
@@ -4656,16 +4654,16 @@
         <v>26</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>31</v>
@@ -4677,7 +4675,7 @@
         <v>32</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>34</v>
@@ -4691,16 +4689,16 @@
         <v>26</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>31</v>
@@ -4712,7 +4710,7 @@
         <v>32</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>34</v>
@@ -4726,16 +4724,16 @@
         <v>26</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>31</v>
@@ -4747,7 +4745,7 @@
         <v>32</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>34</v>
@@ -4761,16 +4759,16 @@
         <v>26</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -4782,7 +4780,7 @@
         <v>32</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>34</v>
@@ -4796,16 +4794,16 @@
         <v>26</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>31</v>
@@ -4817,7 +4815,7 @@
         <v>32</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>34</v>
@@ -4831,16 +4829,16 @@
         <v>26</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>31</v>
@@ -4852,7 +4850,7 @@
         <v>32</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>34</v>
@@ -4866,16 +4864,16 @@
         <v>26</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>31</v>
@@ -4887,7 +4885,7 @@
         <v>32</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>34</v>
@@ -4901,16 +4899,16 @@
         <v>26</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -4922,7 +4920,7 @@
         <v>32</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>34</v>
@@ -4936,16 +4934,16 @@
         <v>26</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>31</v>
@@ -4957,7 +4955,7 @@
         <v>32</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>34</v>
@@ -4971,16 +4969,16 @@
         <v>26</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>31</v>
@@ -4992,7 +4990,7 @@
         <v>32</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>34</v>
@@ -5006,16 +5004,16 @@
         <v>26</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>31</v>
@@ -5027,7 +5025,7 @@
         <v>32</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>34</v>
@@ -5041,16 +5039,16 @@
         <v>26</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -5062,7 +5060,7 @@
         <v>32</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>34</v>
@@ -5076,16 +5074,16 @@
         <v>26</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>31</v>
@@ -5097,7 +5095,7 @@
         <v>32</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>34</v>
@@ -5111,16 +5109,16 @@
         <v>26</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>31</v>
@@ -5132,7 +5130,7 @@
         <v>32</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>34</v>
@@ -5146,16 +5144,16 @@
         <v>26</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>31</v>
@@ -5167,7 +5165,7 @@
         <v>32</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>34</v>
@@ -5181,16 +5179,16 @@
         <v>26</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -5202,7 +5200,7 @@
         <v>32</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>34</v>
@@ -5216,16 +5214,16 @@
         <v>26</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>31</v>
@@ -5237,7 +5235,7 @@
         <v>32</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>34</v>
@@ -5251,16 +5249,16 @@
         <v>26</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -5272,7 +5270,7 @@
         <v>32</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>34</v>
@@ -5286,16 +5284,16 @@
         <v>26</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>31</v>
@@ -5307,7 +5305,7 @@
         <v>32</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>34</v>
@@ -5321,16 +5319,16 @@
         <v>26</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>31</v>
@@ -5342,7 +5340,7 @@
         <v>32</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>34</v>
@@ -5356,16 +5354,16 @@
         <v>26</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>31</v>
@@ -5377,7 +5375,7 @@
         <v>32</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>34</v>
@@ -5391,28 +5389,26 @@
         <v>26</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="8">
-        <v>39</v>
-      </c>
+      <c r="G67" s="8"/>
       <c r="H67" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>34</v>
@@ -5426,16 +5422,16 @@
         <v>26</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>31</v>
@@ -5447,7 +5443,7 @@
         <v>32</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>34</v>
@@ -5461,16 +5457,16 @@
         <v>26</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>31</v>
@@ -5482,7 +5478,7 @@
         <v>32</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J69" s="8" t="s">
         <v>34</v>
@@ -5496,28 +5492,26 @@
         <v>26</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G70" s="11">
-        <v>39</v>
-      </c>
+      <c r="G70" s="8"/>
       <c r="H70" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>34</v>
@@ -5531,28 +5525,26 @@
         <v>26</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G71" s="8">
-        <v>39</v>
-      </c>
+      <c r="G71" s="8"/>
       <c r="H71" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J71" s="8" t="s">
         <v>34</v>
@@ -5566,16 +5558,16 @@
         <v>26</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>31</v>
@@ -5587,7 +5579,7 @@
         <v>32</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>34</v>
@@ -5601,16 +5593,16 @@
         <v>26</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>31</v>
@@ -5622,7 +5614,7 @@
         <v>32</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>34</v>
@@ -5636,16 +5628,16 @@
         <v>26</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>31</v>
@@ -5657,7 +5649,7 @@
         <v>32</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>34</v>
@@ -5671,16 +5663,16 @@
         <v>26</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -5692,7 +5684,7 @@
         <v>32</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>34</v>
@@ -5706,16 +5698,16 @@
         <v>26</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>31</v>
@@ -5727,7 +5719,7 @@
         <v>32</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>34</v>
@@ -5741,16 +5733,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>31</v>
@@ -5762,7 +5754,7 @@
         <v>32</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>34</v>
@@ -5776,16 +5768,16 @@
         <v>26</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>31</v>
@@ -5797,7 +5789,7 @@
         <v>32</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>34</v>
@@ -5811,16 +5803,16 @@
         <v>26</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -5832,7 +5824,7 @@
         <v>32</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>34</v>
@@ -5846,16 +5838,16 @@
         <v>26</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>31</v>
@@ -5867,7 +5859,7 @@
         <v>32</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>34</v>
@@ -5881,16 +5873,16 @@
         <v>26</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>31</v>
@@ -5902,7 +5894,7 @@
         <v>32</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>34</v>
@@ -5916,16 +5908,16 @@
         <v>26</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>31</v>
@@ -5937,7 +5929,7 @@
         <v>32</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>34</v>
@@ -5951,16 +5943,16 @@
         <v>26</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -5972,7 +5964,7 @@
         <v>32</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>34</v>
@@ -5986,16 +5978,16 @@
         <v>26</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>31</v>
@@ -6007,7 +5999,7 @@
         <v>32</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>34</v>
@@ -6021,16 +6013,16 @@
         <v>26</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>31</v>
@@ -6042,7 +6034,7 @@
         <v>32</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>34</v>
@@ -6056,16 +6048,16 @@
         <v>26</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>31</v>
@@ -6077,7 +6069,7 @@
         <v>32</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>34</v>
@@ -6091,16 +6083,16 @@
         <v>26</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -6112,7 +6104,7 @@
         <v>32</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>34</v>
@@ -6126,16 +6118,16 @@
         <v>26</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>31</v>
@@ -6147,7 +6139,7 @@
         <v>32</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>34</v>
@@ -6161,16 +6153,16 @@
         <v>26</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>31</v>
@@ -6182,7 +6174,7 @@
         <v>32</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>34</v>
@@ -6196,16 +6188,16 @@
         <v>26</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>31</v>
@@ -6217,7 +6209,7 @@
         <v>32</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>34</v>
@@ -6231,16 +6223,16 @@
         <v>26</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -6252,7 +6244,7 @@
         <v>32</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>34</v>
@@ -6266,16 +6258,16 @@
         <v>26</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>31</v>
@@ -6287,7 +6279,7 @@
         <v>32</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>34</v>
@@ -6301,16 +6293,16 @@
         <v>26</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -6322,7 +6314,7 @@
         <v>32</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>34</v>
@@ -6336,16 +6328,16 @@
         <v>26</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>31</v>
@@ -6357,7 +6349,7 @@
         <v>32</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>34</v>
@@ -6371,16 +6363,16 @@
         <v>26</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>31</v>
@@ -6392,7 +6384,7 @@
         <v>32</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>34</v>
@@ -6406,16 +6398,16 @@
         <v>26</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>31</v>
@@ -6427,7 +6419,7 @@
         <v>32</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>34</v>
@@ -6441,16 +6433,16 @@
         <v>26</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -6462,7 +6454,7 @@
         <v>32</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>34</v>
@@ -6476,16 +6468,16 @@
         <v>26</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>31</v>
@@ -6497,7 +6489,7 @@
         <v>32</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>34</v>
@@ -6511,16 +6503,16 @@
         <v>26</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>31</v>
@@ -6532,7 +6524,7 @@
         <v>32</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>34</v>
@@ -6546,16 +6538,16 @@
         <v>26</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>31</v>
@@ -6567,7 +6559,7 @@
         <v>32</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>34</v>
@@ -6581,16 +6573,16 @@
         <v>26</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -6602,7 +6594,7 @@
         <v>32</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>34</v>
@@ -6616,16 +6608,16 @@
         <v>26</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>31</v>
@@ -6637,7 +6629,7 @@
         <v>32</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>34</v>
@@ -6651,16 +6643,16 @@
         <v>26</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>31</v>
@@ -6672,7 +6664,7 @@
         <v>32</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>34</v>
@@ -6686,16 +6678,16 @@
         <v>26</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>31</v>
@@ -6707,7 +6699,7 @@
         <v>32</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>34</v>
@@ -6721,16 +6713,16 @@
         <v>26</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -6742,7 +6734,7 @@
         <v>32</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>34</v>
@@ -6756,16 +6748,16 @@
         <v>26</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>31</v>
@@ -6777,7 +6769,7 @@
         <v>32</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>34</v>
@@ -6791,16 +6783,16 @@
         <v>26</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>31</v>
@@ -6812,7 +6804,7 @@
         <v>32</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>34</v>
@@ -6826,16 +6818,16 @@
         <v>26</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>31</v>
@@ -6847,7 +6839,7 @@
         <v>32</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>34</v>
@@ -6861,16 +6853,16 @@
         <v>26</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -6882,7 +6874,7 @@
         <v>32</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J109" s="8" t="s">
         <v>34</v>
@@ -6896,16 +6888,16 @@
         <v>26</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>31</v>
@@ -6917,7 +6909,7 @@
         <v>32</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>34</v>
@@ -6931,16 +6923,16 @@
         <v>26</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>31</v>
@@ -6952,7 +6944,7 @@
         <v>32</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J111" s="8" t="s">
         <v>34</v>
@@ -6966,19 +6958,19 @@
         <v>26</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G112" s="11">
         <v>69</v>
@@ -6987,7 +6979,7 @@
         <v>32</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>34</v>
@@ -7001,19 +6993,19 @@
         <v>26</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G113" s="8">
         <v>69</v>
@@ -7022,7 +7014,7 @@
         <v>32</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>34</v>
@@ -7036,19 +7028,19 @@
         <v>26</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G114" s="11">
         <v>69</v>
@@ -7057,7 +7049,7 @@
         <v>32</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>34</v>
@@ -7071,19 +7063,19 @@
         <v>26</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G115" s="8">
         <v>69</v>
@@ -7092,7 +7084,7 @@
         <v>32</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>34</v>
@@ -7106,19 +7098,19 @@
         <v>26</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G116" s="11">
         <v>69</v>
@@ -7127,7 +7119,7 @@
         <v>32</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>34</v>
@@ -7141,19 +7133,19 @@
         <v>26</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G117" s="8">
         <v>69</v>
@@ -7162,7 +7154,7 @@
         <v>32</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>34</v>
@@ -7176,19 +7168,19 @@
         <v>26</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G118" s="11">
         <v>69</v>
@@ -7197,7 +7189,7 @@
         <v>32</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>34</v>
@@ -7211,19 +7203,19 @@
         <v>26</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G119" s="8">
         <v>69</v>
@@ -7232,7 +7224,7 @@
         <v>32</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>34</v>
@@ -7246,19 +7238,19 @@
         <v>26</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C120" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G120" s="11">
         <v>69</v>
@@ -7267,7 +7259,7 @@
         <v>32</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>34</v>
@@ -7281,19 +7273,19 @@
         <v>26</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G121" s="8">
         <v>69</v>
@@ -7302,7 +7294,7 @@
         <v>32</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>34</v>
@@ -7316,19 +7308,19 @@
         <v>26</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G122" s="11">
         <v>69</v>
@@ -7337,7 +7329,7 @@
         <v>32</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>34</v>
@@ -7351,19 +7343,19 @@
         <v>26</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G123" s="8">
         <v>69</v>
@@ -7372,7 +7364,7 @@
         <v>32</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J123" s="8" t="s">
         <v>34</v>
@@ -7386,19 +7378,19 @@
         <v>26</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G124" s="11">
         <v>69</v>
@@ -7407,7 +7399,7 @@
         <v>32</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>34</v>
@@ -7421,19 +7413,19 @@
         <v>26</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G125" s="8">
         <v>69</v>
@@ -7442,7 +7434,7 @@
         <v>32</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J125" s="8" t="s">
         <v>34</v>
@@ -7456,19 +7448,19 @@
         <v>26</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G126" s="11">
         <v>69</v>
@@ -7477,7 +7469,7 @@
         <v>32</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>34</v>
@@ -7491,19 +7483,19 @@
         <v>26</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G127" s="8">
         <v>69</v>
@@ -7512,7 +7504,7 @@
         <v>32</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>34</v>
@@ -7526,19 +7518,19 @@
         <v>26</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G128" s="11">
         <v>69</v>
@@ -7547,7 +7539,7 @@
         <v>32</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>34</v>
@@ -7561,19 +7553,19 @@
         <v>26</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G129" s="8">
         <v>69</v>
@@ -7582,7 +7574,7 @@
         <v>32</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J129" s="8" t="s">
         <v>34</v>
@@ -7596,19 +7588,19 @@
         <v>26</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G130" s="11">
         <v>69</v>
@@ -7617,7 +7609,7 @@
         <v>32</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>34</v>
@@ -7631,19 +7623,19 @@
         <v>26</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G131" s="8">
         <v>74</v>
@@ -7652,7 +7644,7 @@
         <v>32</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J131" s="8" t="s">
         <v>34</v>
@@ -7666,19 +7658,19 @@
         <v>26</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G132" s="11">
         <v>74</v>
@@ -7687,7 +7679,7 @@
         <v>32</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>34</v>
@@ -7701,19 +7693,19 @@
         <v>26</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G133" s="8">
         <v>74</v>
@@ -7722,7 +7714,7 @@
         <v>32</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J133" s="8" t="s">
         <v>34</v>
@@ -7736,19 +7728,19 @@
         <v>26</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G134" s="11">
         <v>74</v>
@@ -7757,7 +7749,7 @@
         <v>32</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>34</v>
@@ -7771,19 +7763,19 @@
         <v>26</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G135" s="8">
         <v>74</v>
@@ -7792,7 +7784,7 @@
         <v>32</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J135" s="8" t="s">
         <v>34</v>
@@ -7806,19 +7798,19 @@
         <v>26</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G136" s="11">
         <v>74</v>
@@ -7827,7 +7819,7 @@
         <v>32</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>34</v>
@@ -7841,19 +7833,19 @@
         <v>26</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G137" s="8">
         <v>74</v>
@@ -7862,7 +7854,7 @@
         <v>32</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J137" s="8" t="s">
         <v>34</v>
@@ -7876,19 +7868,19 @@
         <v>26</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G138" s="11">
         <v>74</v>
@@ -7897,7 +7889,7 @@
         <v>32</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>34</v>
@@ -7911,19 +7903,19 @@
         <v>26</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G139" s="8">
         <v>74</v>
@@ -7932,7 +7924,7 @@
         <v>32</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J139" s="8" t="s">
         <v>34</v>
@@ -7946,19 +7938,19 @@
         <v>26</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G140" s="11">
         <v>74</v>
@@ -7967,7 +7959,7 @@
         <v>32</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>34</v>
@@ -7981,19 +7973,19 @@
         <v>26</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G141" s="8">
         <v>74</v>
@@ -8002,7 +7994,7 @@
         <v>32</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J141" s="8" t="s">
         <v>34</v>
@@ -8016,19 +8008,19 @@
         <v>26</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G142" s="11">
         <v>74</v>
@@ -8037,7 +8029,7 @@
         <v>32</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>34</v>
@@ -8051,19 +8043,19 @@
         <v>26</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G143" s="8">
         <v>74</v>
@@ -8072,7 +8064,7 @@
         <v>32</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J143" s="8" t="s">
         <v>34</v>
@@ -8086,19 +8078,19 @@
         <v>26</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G144" s="11">
         <v>74</v>
@@ -8107,7 +8099,7 @@
         <v>32</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>34</v>
@@ -8121,19 +8113,19 @@
         <v>26</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G145" s="8">
         <v>74</v>
@@ -8142,7 +8134,7 @@
         <v>32</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J145" s="8" t="s">
         <v>34</v>
@@ -8156,19 +8148,19 @@
         <v>26</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G146" s="11">
         <v>74</v>
@@ -8177,7 +8169,7 @@
         <v>32</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>34</v>
@@ -8191,19 +8183,19 @@
         <v>26</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G147" s="8">
         <v>74</v>
@@ -8212,7 +8204,7 @@
         <v>32</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J147" s="8" t="s">
         <v>34</v>
@@ -8226,19 +8218,19 @@
         <v>26</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G148" s="11">
         <v>74</v>
@@ -8247,7 +8239,7 @@
         <v>32</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>34</v>
@@ -8261,10 +8253,10 @@
         <v>26</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>486</v>
@@ -8297,7 +8289,7 @@
         <v>490</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D150" s="11" t="s">
         <v>486</v>
@@ -8330,7 +8322,7 @@
         <v>493</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>486</v>
@@ -8363,7 +8355,7 @@
         <v>496</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D152" s="11" t="s">
         <v>486</v>
@@ -8396,7 +8388,7 @@
         <v>499</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>486</v>
@@ -8429,7 +8421,7 @@
         <v>502</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D154" s="11" t="s">
         <v>486</v>
@@ -8462,7 +8454,7 @@
         <v>505</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>486</v>
@@ -8495,7 +8487,7 @@
         <v>508</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D156" s="11" t="s">
         <v>486</v>
@@ -8528,7 +8520,7 @@
         <v>511</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>486</v>
@@ -8561,7 +8553,7 @@
         <v>514</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="D158" s="11" t="s">
         <v>486</v>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 09:55 UTC</t>
+    <t>2026-10-10 09:58 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="863">
   <si>
     <t>FINNest — BUILD PROGRESS</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Verified daily tasks</t>
   </si>
   <si>
-    <t>0 / 85</t>
+    <t>1 / 85</t>
   </si>
   <si>
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 09:58 UTC</t>
+    <t>2026-10-10 09:59 UTC</t>
   </si>
   <si>
     <t>Source</t>
@@ -1966,6 +1966,9 @@
     <t>Acceptance</t>
   </si>
   <si>
+    <t>☑</t>
+  </si>
+  <si>
     <t>DAY-001</t>
   </si>
   <si>
@@ -1973,6 +1976,9 @@
   </si>
   <si>
     <t>Freeze V1 scope, personas and measurable success criteria</t>
+  </si>
+  <si>
+    <t>Verified Done</t>
   </si>
   <si>
     <t>Reviewed work artifact or documented validation evidence</t>
@@ -2689,7 +2695,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2710,6 +2716,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -9985,35 +9994,35 @@
       </c>
     </row>
     <row r="5" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>26</v>
+      <c r="A5" s="12" t="s">
+        <v>650</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>32</v>
+        <v>654</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10024,28 +10033,28 @@
         <v>2</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D6" s="11">
         <v>1</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>34</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10056,28 +10065,28 @@
         <v>3</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10088,28 +10097,28 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D8" s="11">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>34</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10120,22 +10129,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>34</v>
@@ -10152,22 +10161,22 @@
         <v>6</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D10" s="11">
         <v>2</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>34</v>
@@ -10184,22 +10193,22 @@
         <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D11" s="8">
         <v>2</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>34</v>
@@ -10216,22 +10225,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D12" s="11">
         <v>2</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>34</v>
@@ -10248,22 +10257,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D13" s="8">
         <v>2</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>34</v>
@@ -10280,22 +10289,22 @@
         <v>10</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D14" s="11">
         <v>2</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>34</v>
@@ -10312,22 +10321,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D15" s="8">
         <v>3</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>34</v>
@@ -10344,22 +10353,22 @@
         <v>12</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D16" s="11">
         <v>3</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>34</v>
@@ -10376,22 +10385,22 @@
         <v>13</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D17" s="8">
         <v>3</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>34</v>
@@ -10408,22 +10417,22 @@
         <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D18" s="11">
         <v>3</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>34</v>
@@ -10440,22 +10449,22 @@
         <v>15</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D19" s="8">
         <v>3</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>34</v>
@@ -10472,22 +10481,22 @@
         <v>16</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D20" s="11">
         <v>4</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>34</v>
@@ -10504,22 +10513,22 @@
         <v>17</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D21" s="8">
         <v>4</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>34</v>
@@ -10536,22 +10545,22 @@
         <v>18</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D22" s="11">
         <v>4</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>34</v>
@@ -10568,22 +10577,22 @@
         <v>19</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D23" s="8">
         <v>4</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>34</v>
@@ -10600,22 +10609,22 @@
         <v>20</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D24" s="11">
         <v>4</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>34</v>
@@ -10632,22 +10641,22 @@
         <v>21</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D25" s="8">
         <v>5</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>34</v>
@@ -10664,22 +10673,22 @@
         <v>22</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D26" s="11">
         <v>5</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>34</v>
@@ -10696,22 +10705,22 @@
         <v>23</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D27" s="8">
         <v>5</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>34</v>
@@ -10728,22 +10737,22 @@
         <v>24</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D28" s="11">
         <v>5</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>34</v>
@@ -10760,22 +10769,22 @@
         <v>25</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D29" s="8">
         <v>5</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>34</v>
@@ -10792,22 +10801,22 @@
         <v>26</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D30" s="11">
         <v>6</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>34</v>
@@ -10824,22 +10833,22 @@
         <v>27</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D31" s="8">
         <v>6</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>34</v>
@@ -10856,22 +10865,22 @@
         <v>28</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D32" s="11">
         <v>6</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>34</v>
@@ -10888,22 +10897,22 @@
         <v>29</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D33" s="8">
         <v>6</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>34</v>
@@ -10920,22 +10929,22 @@
         <v>30</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D34" s="11">
         <v>6</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>34</v>
@@ -10952,22 +10961,22 @@
         <v>31</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D35" s="8">
         <v>7</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>34</v>
@@ -10984,22 +10993,22 @@
         <v>32</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D36" s="11">
         <v>7</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>34</v>
@@ -11016,22 +11025,22 @@
         <v>33</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D37" s="8">
         <v>7</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>34</v>
@@ -11048,22 +11057,22 @@
         <v>34</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D38" s="11">
         <v>7</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>34</v>
@@ -11080,22 +11089,22 @@
         <v>35</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D39" s="8">
         <v>7</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>34</v>
@@ -11112,22 +11121,22 @@
         <v>36</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D40" s="11">
         <v>8</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>34</v>
@@ -11144,22 +11153,22 @@
         <v>37</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D41" s="8">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>34</v>
@@ -11176,22 +11185,22 @@
         <v>38</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D42" s="11">
         <v>8</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>34</v>
@@ -11208,22 +11217,22 @@
         <v>39</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D43" s="8">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>34</v>
@@ -11240,22 +11249,22 @@
         <v>40</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D44" s="11">
         <v>8</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>34</v>
@@ -11272,22 +11281,22 @@
         <v>41</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D45" s="8">
         <v>9</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>34</v>
@@ -11304,22 +11313,22 @@
         <v>42</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D46" s="11">
         <v>9</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>34</v>
@@ -11336,22 +11345,22 @@
         <v>43</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D47" s="8">
         <v>9</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>34</v>
@@ -11368,22 +11377,22 @@
         <v>44</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D48" s="11">
         <v>9</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>34</v>
@@ -11400,22 +11409,22 @@
         <v>45</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D49" s="8">
         <v>9</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>34</v>
@@ -11432,22 +11441,22 @@
         <v>46</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D50" s="11">
         <v>10</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>34</v>
@@ -11464,22 +11473,22 @@
         <v>47</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D51" s="8">
         <v>10</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>34</v>
@@ -11496,22 +11505,22 @@
         <v>48</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D52" s="11">
         <v>10</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>34</v>
@@ -11528,22 +11537,22 @@
         <v>49</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D53" s="8">
         <v>10</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>34</v>
@@ -11560,22 +11569,22 @@
         <v>50</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D54" s="11">
         <v>10</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>34</v>
@@ -11592,22 +11601,22 @@
         <v>51</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D55" s="8">
         <v>11</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>34</v>
@@ -11624,22 +11633,22 @@
         <v>52</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D56" s="11">
         <v>11</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>34</v>
@@ -11656,22 +11665,22 @@
         <v>53</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D57" s="8">
         <v>11</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>34</v>
@@ -11688,22 +11697,22 @@
         <v>54</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D58" s="11">
         <v>11</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>34</v>
@@ -11720,22 +11729,22 @@
         <v>55</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D59" s="8">
         <v>11</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>34</v>
@@ -11752,22 +11761,22 @@
         <v>56</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D60" s="11">
         <v>12</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>34</v>
@@ -11784,22 +11793,22 @@
         <v>57</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D61" s="8">
         <v>12</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>34</v>
@@ -11816,22 +11825,22 @@
         <v>58</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D62" s="11">
         <v>12</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>34</v>
@@ -11848,22 +11857,22 @@
         <v>59</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D63" s="8">
         <v>12</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>34</v>
@@ -11880,22 +11889,22 @@
         <v>60</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D64" s="11">
         <v>12</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>34</v>
@@ -11912,22 +11921,22 @@
         <v>61</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D65" s="8">
         <v>13</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>34</v>
@@ -11944,22 +11953,22 @@
         <v>62</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D66" s="11">
         <v>13</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>34</v>
@@ -11976,22 +11985,22 @@
         <v>63</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D67" s="8">
         <v>13</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="G67" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>34</v>
@@ -12008,22 +12017,22 @@
         <v>64</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D68" s="11">
         <v>13</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>34</v>
@@ -12040,22 +12049,22 @@
         <v>65</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D69" s="8">
         <v>13</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>34</v>
@@ -12072,22 +12081,22 @@
         <v>66</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D70" s="11">
         <v>14</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>34</v>
@@ -12104,22 +12113,22 @@
         <v>67</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D71" s="8">
         <v>14</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>34</v>
@@ -12136,22 +12145,22 @@
         <v>68</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D72" s="11">
         <v>14</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>34</v>
@@ -12168,22 +12177,22 @@
         <v>69</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D73" s="8">
         <v>14</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>34</v>
@@ -12200,22 +12209,22 @@
         <v>70</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D74" s="11">
         <v>14</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G74" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>34</v>
@@ -12232,22 +12241,22 @@
         <v>71</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D75" s="8">
         <v>15</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>34</v>
@@ -12264,22 +12273,22 @@
         <v>72</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D76" s="11">
         <v>15</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="G76" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>34</v>
@@ -12296,22 +12305,22 @@
         <v>73</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D77" s="8">
         <v>15</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>34</v>
@@ -12328,22 +12337,22 @@
         <v>74</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D78" s="11">
         <v>15</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G78" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>34</v>
@@ -12360,22 +12369,22 @@
         <v>75</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D79" s="8">
         <v>15</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G79" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>34</v>
@@ -12392,22 +12401,22 @@
         <v>76</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D80" s="11">
         <v>16</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="G80" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>34</v>
@@ -12424,22 +12433,22 @@
         <v>77</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D81" s="8">
         <v>16</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>34</v>
@@ -12456,22 +12465,22 @@
         <v>78</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D82" s="11">
         <v>16</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G82" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>34</v>
@@ -12488,22 +12497,22 @@
         <v>79</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D83" s="8">
         <v>16</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="G83" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>34</v>
@@ -12520,22 +12529,22 @@
         <v>80</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D84" s="11">
         <v>16</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G84" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>34</v>
@@ -12552,22 +12561,22 @@
         <v>81</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D85" s="8">
         <v>17</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>34</v>
@@ -12584,22 +12593,22 @@
         <v>82</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D86" s="11">
         <v>17</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G86" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>34</v>
@@ -12616,22 +12625,22 @@
         <v>83</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D87" s="8">
         <v>17</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>34</v>
@@ -12648,22 +12657,22 @@
         <v>84</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D88" s="11">
         <v>17</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G88" s="11" t="s">
         <v>32</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>34</v>
@@ -12680,22 +12689,22 @@
         <v>85</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D89" s="8">
         <v>17</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>32</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>34</v>
@@ -12726,80 +12735,80 @@
   <sheetData>
     <row r="1" ht="37" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>843</v>
+      <c r="A3" s="13" t="s">
+        <v>845</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>845</v>
+      <c r="A4" s="13" t="s">
+        <v>847</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>847</v>
+      <c r="A5" s="13" t="s">
+        <v>849</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>849</v>
+      <c r="A6" s="13" t="s">
+        <v>851</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>851</v>
+      <c r="A7" s="13" t="s">
+        <v>853</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>853</v>
+      <c r="A8" s="13" t="s">
+        <v>855</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>855</v>
+      <c r="A9" s="13" t="s">
+        <v>857</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>857</v>
+      <c r="A10" s="13" t="s">
+        <v>859</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>859</v>
+      <c r="A11" s="13" t="s">
+        <v>861</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-10 09:59 UTC</t>
+    <t>2026-10-11 08:50 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 08:50 UTC</t>
+    <t>2026-10-11 08:51 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -37,13 +37,13 @@
     <t>Verified daily tasks</t>
   </si>
   <si>
-    <t>1 / 85</t>
+    <t>2 / 85</t>
   </si>
   <si>
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 08:51 UTC</t>
+    <t>2026-10-11 08:52 UTC</t>
   </si>
   <si>
     <t>Source</t>
@@ -2695,7 +2695,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2719,6 +2719,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -10026,8 +10029,8 @@
       </c>
     </row>
     <row r="6" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>26</v>
+      <c r="A6" s="13" t="s">
+        <v>650</v>
       </c>
       <c r="B6" s="11">
         <v>2</v>
@@ -10045,7 +10048,7 @@
         <v>658</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>32</v>
+        <v>654</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>655</v>
@@ -12740,7 +12743,7 @@
       <c r="B1" s="5"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>845</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -12748,7 +12751,7 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>847</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -12756,7 +12759,7 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>849</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -12764,7 +12767,7 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>851</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -12772,7 +12775,7 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>853</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -12780,7 +12783,7 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>855</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -12788,7 +12791,7 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>857</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -12796,7 +12799,7 @@
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>859</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -12804,7 +12807,7 @@
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>861</v>
       </c>
       <c r="B11" s="8" t="s">

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 08:52 UTC</t>
+    <t>2026-10-11 10:01 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -37,7 +37,7 @@
     <t>Verified daily tasks</t>
   </si>
   <si>
-    <t>2 / 85</t>
+    <t>3 / 85</t>
   </si>
   <si>
     <t>Last synchronized (UTC)</t>
@@ -10061,8 +10061,8 @@
       </c>
     </row>
     <row r="7" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>26</v>
+      <c r="A7" s="12" t="s">
+        <v>650</v>
       </c>
       <c r="B7" s="8">
         <v>3</v>
@@ -10080,7 +10080,7 @@
         <v>661</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>32</v>
+        <v>654</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>655</v>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 10:01 UTC</t>
+    <t>2026-10-11 16:53 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -37,7 +37,7 @@
     <t>Verified daily tasks</t>
   </si>
   <si>
-    <t>3 / 85</t>
+    <t>4 / 85</t>
   </si>
   <si>
     <t>Last synchronized (UTC)</t>
@@ -10093,8 +10093,8 @@
       </c>
     </row>
     <row r="8" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>26</v>
+      <c r="A8" s="13" t="s">
+        <v>650</v>
       </c>
       <c r="B8" s="11">
         <v>4</v>
@@ -10112,7 +10112,7 @@
         <v>664</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>32</v>
+        <v>654</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>655</v>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 16:53 UTC</t>
+    <t>2026-10-11 16:54 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 16:54 UTC</t>
+    <t>2026-10-11 21:52 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -28,7 +28,7 @@
     <t>Verified V1 features</t>
   </si>
   <si>
-    <t>0 / 140</t>
+    <t>1 / 140</t>
   </si>
   <si>
     <t>V1 feature progress</t>
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 21:52 UTC</t>
+    <t>2026-10-11 21:53 UTC</t>
   </si>
   <si>
     <t>Source</t>
@@ -160,12 +160,18 @@
     <t>https://github.com/Tejanshu22/PersonalFinanceManager/issues/5</t>
   </si>
   <si>
+    <t>☑</t>
+  </si>
+  <si>
     <t>FIN-005</t>
   </si>
   <si>
     <t>Brand configuration and rename policy</t>
   </si>
   <si>
+    <t>Verified Done</t>
+  </si>
+  <si>
     <t>Display name comes only from config and rebrand guide exists</t>
   </si>
   <si>
@@ -1966,9 +1972,6 @@
     <t>Acceptance</t>
   </si>
   <si>
-    <t>☑</t>
-  </si>
-  <si>
     <t>DAY-001</t>
   </si>
   <si>
@@ -1976,9 +1979,6 @@
   </si>
   <si>
     <t>Freeze V1 scope, personas and measurable success criteria</t>
-  </si>
-  <si>
-    <t>Verified Done</t>
   </si>
   <si>
     <t>Reviewed work artifact or documented validation evidence</t>
@@ -3100,7 +3100,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>0.007142857142857143</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3369,11 +3369,11 @@
       </c>
     </row>
     <row r="9" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>26</v>
+      <c r="A9" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>28</v>
@@ -3382,7 +3382,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>31</v>
@@ -3391,16 +3391,16 @@
         <v>1</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3408,7 +3408,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>28</v>
@@ -3417,7 +3417,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>31</v>
@@ -3429,13 +3429,13 @@
         <v>32</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3443,7 +3443,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>28</v>
@@ -3452,7 +3452,7 @@
         <v>29</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>31</v>
@@ -3464,13 +3464,13 @@
         <v>32</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3478,7 +3478,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>28</v>
@@ -3487,7 +3487,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>31</v>
@@ -3499,13 +3499,13 @@
         <v>32</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3513,16 +3513,16 @@
         <v>26</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>31</v>
@@ -3534,13 +3534,13 @@
         <v>32</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3548,16 +3548,16 @@
         <v>26</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>31</v>
@@ -3569,13 +3569,13 @@
         <v>32</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3583,16 +3583,16 @@
         <v>26</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>31</v>
@@ -3604,13 +3604,13 @@
         <v>32</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3618,16 +3618,16 @@
         <v>26</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>31</v>
@@ -3639,13 +3639,13 @@
         <v>32</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3653,16 +3653,16 @@
         <v>26</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>31</v>
@@ -3674,13 +3674,13 @@
         <v>32</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3688,16 +3688,16 @@
         <v>26</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>31</v>
@@ -3709,13 +3709,13 @@
         <v>32</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3723,16 +3723,16 @@
         <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>31</v>
@@ -3744,13 +3744,13 @@
         <v>32</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3758,16 +3758,16 @@
         <v>26</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>31</v>
@@ -3779,13 +3779,13 @@
         <v>32</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3793,16 +3793,16 @@
         <v>26</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>31</v>
@@ -3814,13 +3814,13 @@
         <v>32</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3828,16 +3828,16 @@
         <v>26</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>31</v>
@@ -3849,13 +3849,13 @@
         <v>32</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3863,16 +3863,16 @@
         <v>26</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>31</v>
@@ -3884,13 +3884,13 @@
         <v>32</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3898,16 +3898,16 @@
         <v>26</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>31</v>
@@ -3919,13 +3919,13 @@
         <v>32</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3933,16 +3933,16 @@
         <v>26</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>31</v>
@@ -3954,13 +3954,13 @@
         <v>32</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3968,16 +3968,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>31</v>
@@ -3989,13 +3989,13 @@
         <v>32</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4003,16 +4003,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>31</v>
@@ -4024,13 +4024,13 @@
         <v>32</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4038,16 +4038,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>31</v>
@@ -4059,13 +4059,13 @@
         <v>32</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4073,16 +4073,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>31</v>
@@ -4094,13 +4094,13 @@
         <v>32</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4108,16 +4108,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>31</v>
@@ -4129,13 +4129,13 @@
         <v>32</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4143,16 +4143,16 @@
         <v>26</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>31</v>
@@ -4162,13 +4162,13 @@
         <v>32</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4176,16 +4176,16 @@
         <v>26</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>31</v>
@@ -4197,13 +4197,13 @@
         <v>32</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4211,16 +4211,16 @@
         <v>26</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>31</v>
@@ -4232,13 +4232,13 @@
         <v>32</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4246,16 +4246,16 @@
         <v>26</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>31</v>
@@ -4267,13 +4267,13 @@
         <v>32</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4281,16 +4281,16 @@
         <v>26</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>31</v>
@@ -4302,13 +4302,13 @@
         <v>32</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4316,16 +4316,16 @@
         <v>26</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>31</v>
@@ -4337,13 +4337,13 @@
         <v>32</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4351,16 +4351,16 @@
         <v>26</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>31</v>
@@ -4372,13 +4372,13 @@
         <v>32</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4386,16 +4386,16 @@
         <v>26</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>31</v>
@@ -4407,13 +4407,13 @@
         <v>32</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4421,16 +4421,16 @@
         <v>26</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>31</v>
@@ -4442,13 +4442,13 @@
         <v>32</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4456,16 +4456,16 @@
         <v>26</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>31</v>
@@ -4477,13 +4477,13 @@
         <v>32</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4491,16 +4491,16 @@
         <v>26</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>31</v>
@@ -4512,13 +4512,13 @@
         <v>32</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4526,16 +4526,16 @@
         <v>26</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>31</v>
@@ -4547,13 +4547,13 @@
         <v>32</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4561,16 +4561,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>31</v>
@@ -4582,13 +4582,13 @@
         <v>32</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4596,16 +4596,16 @@
         <v>26</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>31</v>
@@ -4617,13 +4617,13 @@
         <v>32</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4631,16 +4631,16 @@
         <v>26</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>31</v>
@@ -4652,13 +4652,13 @@
         <v>32</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4666,16 +4666,16 @@
         <v>26</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>31</v>
@@ -4687,13 +4687,13 @@
         <v>32</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4701,16 +4701,16 @@
         <v>26</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>31</v>
@@ -4722,13 +4722,13 @@
         <v>32</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4736,16 +4736,16 @@
         <v>26</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>31</v>
@@ -4757,13 +4757,13 @@
         <v>32</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4771,16 +4771,16 @@
         <v>26</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>31</v>
@@ -4792,13 +4792,13 @@
         <v>32</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4806,16 +4806,16 @@
         <v>26</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>31</v>
@@ -4827,13 +4827,13 @@
         <v>32</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4841,16 +4841,16 @@
         <v>26</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>31</v>
@@ -4862,13 +4862,13 @@
         <v>32</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4876,16 +4876,16 @@
         <v>26</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>31</v>
@@ -4897,13 +4897,13 @@
         <v>32</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4911,16 +4911,16 @@
         <v>26</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>31</v>
@@ -4932,13 +4932,13 @@
         <v>32</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4946,16 +4946,16 @@
         <v>26</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>31</v>
@@ -4967,13 +4967,13 @@
         <v>32</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4981,16 +4981,16 @@
         <v>26</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>31</v>
@@ -5002,13 +5002,13 @@
         <v>32</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5016,16 +5016,16 @@
         <v>26</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>31</v>
@@ -5037,13 +5037,13 @@
         <v>32</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5051,16 +5051,16 @@
         <v>26</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>31</v>
@@ -5072,13 +5072,13 @@
         <v>32</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5086,16 +5086,16 @@
         <v>26</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>31</v>
@@ -5107,13 +5107,13 @@
         <v>32</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5121,16 +5121,16 @@
         <v>26</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>31</v>
@@ -5142,13 +5142,13 @@
         <v>32</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5156,16 +5156,16 @@
         <v>26</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>31</v>
@@ -5177,13 +5177,13 @@
         <v>32</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5191,16 +5191,16 @@
         <v>26</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>31</v>
@@ -5212,13 +5212,13 @@
         <v>32</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5226,16 +5226,16 @@
         <v>26</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>31</v>
@@ -5247,13 +5247,13 @@
         <v>32</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5261,16 +5261,16 @@
         <v>26</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>31</v>
@@ -5282,13 +5282,13 @@
         <v>32</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5296,16 +5296,16 @@
         <v>26</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>31</v>
@@ -5317,13 +5317,13 @@
         <v>32</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5331,16 +5331,16 @@
         <v>26</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>31</v>
@@ -5352,13 +5352,13 @@
         <v>32</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5366,16 +5366,16 @@
         <v>26</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>31</v>
@@ -5387,13 +5387,13 @@
         <v>32</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5401,16 +5401,16 @@
         <v>26</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>31</v>
@@ -5420,13 +5420,13 @@
         <v>32</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5434,16 +5434,16 @@
         <v>26</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>31</v>
@@ -5455,13 +5455,13 @@
         <v>32</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5469,16 +5469,16 @@
         <v>26</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>31</v>
@@ -5490,13 +5490,13 @@
         <v>32</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J69" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5504,16 +5504,16 @@
         <v>26</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>31</v>
@@ -5523,13 +5523,13 @@
         <v>32</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5537,16 +5537,16 @@
         <v>26</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>31</v>
@@ -5556,13 +5556,13 @@
         <v>32</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J71" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K71" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5570,16 +5570,16 @@
         <v>26</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>31</v>
@@ -5591,13 +5591,13 @@
         <v>32</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5605,16 +5605,16 @@
         <v>26</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>31</v>
@@ -5626,13 +5626,13 @@
         <v>32</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5640,16 +5640,16 @@
         <v>26</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>31</v>
@@ -5661,13 +5661,13 @@
         <v>32</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5675,16 +5675,16 @@
         <v>26</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>31</v>
@@ -5696,13 +5696,13 @@
         <v>32</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5710,16 +5710,16 @@
         <v>26</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>31</v>
@@ -5731,13 +5731,13 @@
         <v>32</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5745,16 +5745,16 @@
         <v>26</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>31</v>
@@ -5766,13 +5766,13 @@
         <v>32</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5780,16 +5780,16 @@
         <v>26</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>31</v>
@@ -5801,13 +5801,13 @@
         <v>32</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5815,16 +5815,16 @@
         <v>26</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>31</v>
@@ -5836,13 +5836,13 @@
         <v>32</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5850,16 +5850,16 @@
         <v>26</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>31</v>
@@ -5871,13 +5871,13 @@
         <v>32</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5885,16 +5885,16 @@
         <v>26</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>31</v>
@@ -5906,13 +5906,13 @@
         <v>32</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5920,16 +5920,16 @@
         <v>26</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>31</v>
@@ -5941,13 +5941,13 @@
         <v>32</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5955,16 +5955,16 @@
         <v>26</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>31</v>
@@ -5976,13 +5976,13 @@
         <v>32</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5990,16 +5990,16 @@
         <v>26</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>31</v>
@@ -6011,13 +6011,13 @@
         <v>32</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6025,16 +6025,16 @@
         <v>26</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>31</v>
@@ -6046,13 +6046,13 @@
         <v>32</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6060,16 +6060,16 @@
         <v>26</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>31</v>
@@ -6081,13 +6081,13 @@
         <v>32</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6095,16 +6095,16 @@
         <v>26</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>31</v>
@@ -6116,13 +6116,13 @@
         <v>32</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6130,16 +6130,16 @@
         <v>26</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>31</v>
@@ -6151,13 +6151,13 @@
         <v>32</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6165,16 +6165,16 @@
         <v>26</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>31</v>
@@ -6186,13 +6186,13 @@
         <v>32</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6200,16 +6200,16 @@
         <v>26</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>31</v>
@@ -6221,13 +6221,13 @@
         <v>32</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6235,16 +6235,16 @@
         <v>26</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>31</v>
@@ -6256,13 +6256,13 @@
         <v>32</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6270,16 +6270,16 @@
         <v>26</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>31</v>
@@ -6291,13 +6291,13 @@
         <v>32</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6305,16 +6305,16 @@
         <v>26</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>31</v>
@@ -6326,13 +6326,13 @@
         <v>32</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6340,16 +6340,16 @@
         <v>26</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>31</v>
@@ -6361,13 +6361,13 @@
         <v>32</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6375,16 +6375,16 @@
         <v>26</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>31</v>
@@ -6396,13 +6396,13 @@
         <v>32</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6410,16 +6410,16 @@
         <v>26</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>31</v>
@@ -6431,13 +6431,13 @@
         <v>32</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6445,16 +6445,16 @@
         <v>26</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>31</v>
@@ -6466,13 +6466,13 @@
         <v>32</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6480,16 +6480,16 @@
         <v>26</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>31</v>
@@ -6501,13 +6501,13 @@
         <v>32</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6515,16 +6515,16 @@
         <v>26</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>31</v>
@@ -6536,13 +6536,13 @@
         <v>32</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6550,16 +6550,16 @@
         <v>26</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>31</v>
@@ -6571,13 +6571,13 @@
         <v>32</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6585,16 +6585,16 @@
         <v>26</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>31</v>
@@ -6606,13 +6606,13 @@
         <v>32</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6620,16 +6620,16 @@
         <v>26</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>31</v>
@@ -6641,13 +6641,13 @@
         <v>32</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K102" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6655,16 +6655,16 @@
         <v>26</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>31</v>
@@ -6676,13 +6676,13 @@
         <v>32</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6690,16 +6690,16 @@
         <v>26</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>31</v>
@@ -6711,13 +6711,13 @@
         <v>32</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6725,16 +6725,16 @@
         <v>26</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>31</v>
@@ -6746,13 +6746,13 @@
         <v>32</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6760,16 +6760,16 @@
         <v>26</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>31</v>
@@ -6781,13 +6781,13 @@
         <v>32</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6795,16 +6795,16 @@
         <v>26</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>31</v>
@@ -6816,13 +6816,13 @@
         <v>32</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K107" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6830,16 +6830,16 @@
         <v>26</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>31</v>
@@ -6851,13 +6851,13 @@
         <v>32</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6865,16 +6865,16 @@
         <v>26</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>31</v>
@@ -6886,13 +6886,13 @@
         <v>32</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J109" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K109" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6900,16 +6900,16 @@
         <v>26</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>31</v>
@@ -6921,13 +6921,13 @@
         <v>32</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="111" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6935,16 +6935,16 @@
         <v>26</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>31</v>
@@ -6956,13 +6956,13 @@
         <v>32</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J111" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6970,19 +6970,19 @@
         <v>26</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G112" s="11">
         <v>69</v>
@@ -6991,13 +6991,13 @@
         <v>32</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K112" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="113" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7005,19 +7005,19 @@
         <v>26</v>
       </c>
       <c r="B113" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F113" s="8" t="s">
         <v>376</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>374</v>
       </c>
       <c r="G113" s="8">
         <v>69</v>
@@ -7026,13 +7026,13 @@
         <v>32</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7040,19 +7040,19 @@
         <v>26</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G114" s="11">
         <v>69</v>
@@ -7061,13 +7061,13 @@
         <v>32</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K114" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7075,19 +7075,19 @@
         <v>26</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G115" s="8">
         <v>69</v>
@@ -7096,13 +7096,13 @@
         <v>32</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K115" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7110,19 +7110,19 @@
         <v>26</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G116" s="11">
         <v>69</v>
@@ -7131,13 +7131,13 @@
         <v>32</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K116" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7145,19 +7145,19 @@
         <v>26</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G117" s="8">
         <v>69</v>
@@ -7166,13 +7166,13 @@
         <v>32</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K117" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7180,19 +7180,19 @@
         <v>26</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G118" s="11">
         <v>69</v>
@@ -7201,13 +7201,13 @@
         <v>32</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7215,19 +7215,19 @@
         <v>26</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G119" s="8">
         <v>69</v>
@@ -7236,13 +7236,13 @@
         <v>32</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K119" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7250,19 +7250,19 @@
         <v>26</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C120" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G120" s="11">
         <v>69</v>
@@ -7271,13 +7271,13 @@
         <v>32</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K120" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7285,19 +7285,19 @@
         <v>26</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G121" s="8">
         <v>69</v>
@@ -7306,13 +7306,13 @@
         <v>32</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K121" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7320,19 +7320,19 @@
         <v>26</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G122" s="11">
         <v>69</v>
@@ -7341,13 +7341,13 @@
         <v>32</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7355,19 +7355,19 @@
         <v>26</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G123" s="8">
         <v>69</v>
@@ -7376,13 +7376,13 @@
         <v>32</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J123" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K123" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7390,19 +7390,19 @@
         <v>26</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G124" s="11">
         <v>69</v>
@@ -7411,13 +7411,13 @@
         <v>32</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K124" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7425,19 +7425,19 @@
         <v>26</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G125" s="8">
         <v>69</v>
@@ -7446,13 +7446,13 @@
         <v>32</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J125" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K125" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7460,19 +7460,19 @@
         <v>26</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G126" s="11">
         <v>69</v>
@@ -7481,13 +7481,13 @@
         <v>32</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K126" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7495,19 +7495,19 @@
         <v>26</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G127" s="8">
         <v>69</v>
@@ -7516,13 +7516,13 @@
         <v>32</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7530,19 +7530,19 @@
         <v>26</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G128" s="11">
         <v>69</v>
@@ -7551,13 +7551,13 @@
         <v>32</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K128" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7565,19 +7565,19 @@
         <v>26</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G129" s="8">
         <v>69</v>
@@ -7586,13 +7586,13 @@
         <v>32</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J129" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K129" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7600,19 +7600,19 @@
         <v>26</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G130" s="11">
         <v>69</v>
@@ -7621,13 +7621,13 @@
         <v>32</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K130" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7635,19 +7635,19 @@
         <v>26</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G131" s="8">
         <v>74</v>
@@ -7656,13 +7656,13 @@
         <v>32</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J131" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K131" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7670,19 +7670,19 @@
         <v>26</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G132" s="11">
         <v>74</v>
@@ -7691,13 +7691,13 @@
         <v>32</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7705,19 +7705,19 @@
         <v>26</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G133" s="8">
         <v>74</v>
@@ -7726,13 +7726,13 @@
         <v>32</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J133" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K133" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7740,19 +7740,19 @@
         <v>26</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G134" s="11">
         <v>74</v>
@@ -7761,13 +7761,13 @@
         <v>32</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K134" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7775,19 +7775,19 @@
         <v>26</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G135" s="8">
         <v>74</v>
@@ -7796,13 +7796,13 @@
         <v>32</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J135" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K135" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7810,19 +7810,19 @@
         <v>26</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G136" s="11">
         <v>74</v>
@@ -7831,13 +7831,13 @@
         <v>32</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K136" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7845,19 +7845,19 @@
         <v>26</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G137" s="8">
         <v>74</v>
@@ -7866,13 +7866,13 @@
         <v>32</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J137" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K137" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="138" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7880,19 +7880,19 @@
         <v>26</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G138" s="11">
         <v>74</v>
@@ -7901,13 +7901,13 @@
         <v>32</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K138" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7915,19 +7915,19 @@
         <v>26</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G139" s="8">
         <v>74</v>
@@ -7936,13 +7936,13 @@
         <v>32</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J139" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K139" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="140" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7950,19 +7950,19 @@
         <v>26</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G140" s="11">
         <v>74</v>
@@ -7971,13 +7971,13 @@
         <v>32</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K140" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -7985,19 +7985,19 @@
         <v>26</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G141" s="8">
         <v>74</v>
@@ -8006,13 +8006,13 @@
         <v>32</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J141" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K141" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="142" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8020,19 +8020,19 @@
         <v>26</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G142" s="11">
         <v>74</v>
@@ -8041,13 +8041,13 @@
         <v>32</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K142" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="143" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8055,19 +8055,19 @@
         <v>26</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G143" s="8">
         <v>74</v>
@@ -8076,13 +8076,13 @@
         <v>32</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J143" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K143" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="144" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8090,19 +8090,19 @@
         <v>26</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G144" s="11">
         <v>74</v>
@@ -8111,13 +8111,13 @@
         <v>32</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K144" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8125,19 +8125,19 @@
         <v>26</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G145" s="8">
         <v>74</v>
@@ -8146,13 +8146,13 @@
         <v>32</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J145" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K145" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8160,19 +8160,19 @@
         <v>26</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G146" s="11">
         <v>74</v>
@@ -8181,13 +8181,13 @@
         <v>32</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K146" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="147" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8195,19 +8195,19 @@
         <v>26</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G147" s="8">
         <v>74</v>
@@ -8216,13 +8216,13 @@
         <v>32</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J147" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K147" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8230,19 +8230,19 @@
         <v>26</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G148" s="11">
         <v>74</v>
@@ -8251,13 +8251,13 @@
         <v>32</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K148" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8265,32 +8265,32 @@
         <v>26</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G149" s="8"/>
       <c r="H149" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J149" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K149" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="150" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8298,32 +8298,32 @@
         <v>26</v>
       </c>
       <c r="B150" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="E150" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="F150" s="11" t="s">
         <v>490</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="E150" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>488</v>
       </c>
       <c r="G150" s="8"/>
       <c r="H150" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I150" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J150" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K150" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8331,32 +8331,32 @@
         <v>26</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G151" s="8"/>
       <c r="H151" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J151" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K151" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="152" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8364,32 +8364,32 @@
         <v>26</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E152" s="11" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G152" s="8"/>
       <c r="H152" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J152" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K152" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="153" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8397,32 +8397,32 @@
         <v>26</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G153" s="8"/>
       <c r="H153" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I153" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J153" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K153" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="154" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8430,32 +8430,32 @@
         <v>26</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G154" s="8"/>
       <c r="H154" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J154" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K154" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8463,32 +8463,32 @@
         <v>26</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G155" s="8"/>
       <c r="H155" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I155" s="8" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J155" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K155" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="156" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8496,32 +8496,32 @@
         <v>26</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E156" s="11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G156" s="8"/>
       <c r="H156" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J156" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K156" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8529,32 +8529,32 @@
         <v>26</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G157" s="8"/>
       <c r="H157" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I157" s="8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J157" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K157" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="158" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8562,32 +8562,32 @@
         <v>26</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E158" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F158" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G158" s="8"/>
       <c r="H158" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J158" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K158" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="159" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8595,32 +8595,32 @@
         <v>26</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G159" s="8"/>
       <c r="H159" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I159" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J159" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K159" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8628,32 +8628,32 @@
         <v>26</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E160" s="11" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G160" s="8"/>
       <c r="H160" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J160" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K160" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8661,32 +8661,32 @@
         <v>26</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G161" s="8"/>
       <c r="H161" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J161" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K161" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8694,32 +8694,32 @@
         <v>26</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G162" s="8"/>
       <c r="H162" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I162" s="11" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J162" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K162" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="163" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8727,32 +8727,32 @@
         <v>26</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G163" s="8"/>
       <c r="H163" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J163" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="164" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8760,32 +8760,32 @@
         <v>26</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G164" s="8"/>
       <c r="H164" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I164" s="11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J164" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K164" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="165" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8793,32 +8793,32 @@
         <v>26</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G165" s="8"/>
       <c r="H165" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J165" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K165" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="166" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8826,32 +8826,32 @@
         <v>26</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G166" s="8"/>
       <c r="H166" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I166" s="11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J166" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K166" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="167" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8859,32 +8859,32 @@
         <v>26</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G167" s="8"/>
       <c r="H167" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J167" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K167" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="168" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8892,32 +8892,32 @@
         <v>26</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E168" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F168" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G168" s="8"/>
       <c r="H168" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J168" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K168" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="169" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8925,32 +8925,32 @@
         <v>26</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G169" s="8"/>
       <c r="H169" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I169" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J169" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K169" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="170" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8958,32 +8958,32 @@
         <v>26</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E170" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F170" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G170" s="8"/>
       <c r="H170" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I170" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J170" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K170" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="171" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8991,32 +8991,32 @@
         <v>26</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G171" s="8"/>
       <c r="H171" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I171" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J171" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K171" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="172" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9024,32 +9024,32 @@
         <v>26</v>
       </c>
       <c r="B172" s="11" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G172" s="8"/>
       <c r="H172" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I172" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J172" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K172" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="173" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9057,32 +9057,32 @@
         <v>26</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G173" s="8"/>
       <c r="H173" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I173" s="8" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J173" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K173" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="174" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9090,32 +9090,32 @@
         <v>26</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E174" s="11" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F174" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G174" s="8"/>
       <c r="H174" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I174" s="11" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J174" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K174" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="175" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9123,32 +9123,32 @@
         <v>26</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G175" s="8"/>
       <c r="H175" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I175" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J175" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K175" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="176" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9156,32 +9156,32 @@
         <v>26</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E176" s="11" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G176" s="8"/>
       <c r="H176" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I176" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J176" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K176" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="177" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9189,32 +9189,32 @@
         <v>26</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G177" s="8"/>
       <c r="H177" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I177" s="8" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J177" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K177" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="178" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9222,32 +9222,32 @@
         <v>26</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E178" s="11" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F178" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G178" s="8"/>
       <c r="H178" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I178" s="11" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J178" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K178" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9255,32 +9255,32 @@
         <v>26</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G179" s="8"/>
       <c r="H179" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I179" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J179" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K179" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9288,32 +9288,32 @@
         <v>26</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E180" s="11" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G180" s="8"/>
       <c r="H180" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I180" s="11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J180" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K180" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="181" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9321,32 +9321,32 @@
         <v>26</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G181" s="8"/>
       <c r="H181" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I181" s="8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J181" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K181" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9354,32 +9354,32 @@
         <v>26</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E182" s="11" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G182" s="8"/>
       <c r="H182" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I182" s="11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J182" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K182" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="183" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9387,32 +9387,32 @@
         <v>26</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G183" s="8"/>
       <c r="H183" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I183" s="8" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J183" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K183" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="184" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9420,32 +9420,32 @@
         <v>26</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G184" s="8"/>
       <c r="H184" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I184" s="11" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J184" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K184" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="185" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9453,32 +9453,32 @@
         <v>26</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="F185" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G185" s="8"/>
       <c r="H185" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I185" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J185" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K185" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="186" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9486,32 +9486,32 @@
         <v>26</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E186" s="11" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G186" s="8"/>
       <c r="H186" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I186" s="11" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J186" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K186" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9519,32 +9519,32 @@
         <v>26</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F187" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G187" s="8"/>
       <c r="H187" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I187" s="8" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J187" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K187" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="188" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9552,32 +9552,32 @@
         <v>26</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E188" s="11" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F188" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G188" s="8"/>
       <c r="H188" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I188" s="11" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J188" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K188" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="189" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9585,32 +9585,32 @@
         <v>26</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="F189" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G189" s="8"/>
       <c r="H189" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I189" s="8" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J189" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K189" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="190" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9618,32 +9618,32 @@
         <v>26</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E190" s="11" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F190" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G190" s="8"/>
       <c r="H190" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I190" s="11" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J190" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K190" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="191" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9651,32 +9651,32 @@
         <v>26</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G191" s="8"/>
       <c r="H191" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I191" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J191" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K191" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="192" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9684,32 +9684,32 @@
         <v>26</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E192" s="11" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G192" s="8"/>
       <c r="H192" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I192" s="11" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J192" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K192" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9717,32 +9717,32 @@
         <v>26</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G193" s="8"/>
       <c r="H193" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I193" s="8" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J193" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K193" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="194" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9750,32 +9750,32 @@
         <v>26</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E194" s="11" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F194" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G194" s="8"/>
       <c r="H194" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I194" s="11" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J194" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K194" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="195" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9783,32 +9783,32 @@
         <v>26</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G195" s="8"/>
       <c r="H195" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I195" s="8" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J195" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K195" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="196" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9816,32 +9816,32 @@
         <v>26</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E196" s="11" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G196" s="8"/>
       <c r="H196" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I196" s="11" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J196" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K196" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="197" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9849,32 +9849,32 @@
         <v>26</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G197" s="8"/>
       <c r="H197" s="8" t="s">
         <v>32</v>
       </c>
       <c r="I197" s="8" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J197" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K197" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="198" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9882,32 +9882,32 @@
         <v>26</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E198" s="11" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F198" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G198" s="8"/>
       <c r="H198" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I198" s="11" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J198" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K198" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -9938,7 +9938,7 @@
   <sheetData>
     <row r="1" ht="35" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -9969,25 +9969,25 @@
         <v>15</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>24</v>
@@ -9998,25 +9998,25 @@
     </row>
     <row r="5" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>650</v>
+        <v>48</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>654</v>
+        <v>51</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>655</v>
@@ -10030,7 +10030,7 @@
     </row>
     <row r="6" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>650</v>
+        <v>48</v>
       </c>
       <c r="B6" s="11">
         <v>2</v>
@@ -10042,13 +10042,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>658</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>654</v>
+        <v>51</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>655</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="7" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>650</v>
+        <v>48</v>
       </c>
       <c r="B7" s="8">
         <v>3</v>
@@ -10074,13 +10074,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>661</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>654</v>
+        <v>51</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>655</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="8" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>650</v>
+        <v>48</v>
       </c>
       <c r="B8" s="11">
         <v>4</v>
@@ -10106,13 +10106,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>664</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>654</v>
+        <v>51</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>655</v>
@@ -10138,7 +10138,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>667</v>
@@ -10153,7 +10153,7 @@
         <v>34</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10185,7 +10185,7 @@
         <v>34</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10217,7 +10217,7 @@
         <v>34</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10249,7 +10249,7 @@
         <v>34</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10281,7 +10281,7 @@
         <v>34</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>34</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
         <v>34</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10377,7 +10377,7 @@
         <v>34</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10409,7 +10409,7 @@
         <v>34</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10441,7 +10441,7 @@
         <v>34</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10473,7 +10473,7 @@
         <v>34</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10505,7 +10505,7 @@
         <v>34</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10537,7 +10537,7 @@
         <v>34</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10569,7 +10569,7 @@
         <v>34</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10601,7 +10601,7 @@
         <v>34</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10633,7 +10633,7 @@
         <v>34</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10665,7 +10665,7 @@
         <v>34</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10697,7 +10697,7 @@
         <v>34</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10729,7 +10729,7 @@
         <v>34</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10761,7 +10761,7 @@
         <v>34</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10793,7 +10793,7 @@
         <v>34</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10825,7 +10825,7 @@
         <v>34</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10857,7 +10857,7 @@
         <v>34</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10889,7 +10889,7 @@
         <v>34</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10921,7 +10921,7 @@
         <v>34</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10953,7 +10953,7 @@
         <v>34</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -10985,7 +10985,7 @@
         <v>34</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11017,7 +11017,7 @@
         <v>34</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11049,7 +11049,7 @@
         <v>34</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11081,7 +11081,7 @@
         <v>34</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
         <v>34</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11145,7 +11145,7 @@
         <v>34</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11177,7 +11177,7 @@
         <v>34</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11209,7 +11209,7 @@
         <v>34</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11241,7 +11241,7 @@
         <v>34</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>34</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11305,7 +11305,7 @@
         <v>34</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11337,7 +11337,7 @@
         <v>34</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11369,7 +11369,7 @@
         <v>34</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11401,7 +11401,7 @@
         <v>34</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11433,7 +11433,7 @@
         <v>34</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11465,7 +11465,7 @@
         <v>34</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11497,7 +11497,7 @@
         <v>34</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11529,7 +11529,7 @@
         <v>34</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11561,7 +11561,7 @@
         <v>34</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11593,7 +11593,7 @@
         <v>34</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11625,7 +11625,7 @@
         <v>34</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11657,7 +11657,7 @@
         <v>34</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11689,7 +11689,7 @@
         <v>34</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11721,7 +11721,7 @@
         <v>34</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11753,7 +11753,7 @@
         <v>34</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11785,7 +11785,7 @@
         <v>34</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11817,7 +11817,7 @@
         <v>34</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11849,7 +11849,7 @@
         <v>34</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11881,7 +11881,7 @@
         <v>34</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11913,7 +11913,7 @@
         <v>34</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11945,7 +11945,7 @@
         <v>34</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11977,7 +11977,7 @@
         <v>34</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12009,7 +12009,7 @@
         <v>34</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12041,7 +12041,7 @@
         <v>34</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12073,7 +12073,7 @@
         <v>34</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12105,7 +12105,7 @@
         <v>34</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12137,7 +12137,7 @@
         <v>34</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12169,7 +12169,7 @@
         <v>34</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12201,7 +12201,7 @@
         <v>34</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12233,7 +12233,7 @@
         <v>34</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12265,7 +12265,7 @@
         <v>34</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12297,7 +12297,7 @@
         <v>34</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12329,7 +12329,7 @@
         <v>34</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12361,7 +12361,7 @@
         <v>34</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12393,7 +12393,7 @@
         <v>34</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12425,7 +12425,7 @@
         <v>34</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12457,7 +12457,7 @@
         <v>34</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12489,7 +12489,7 @@
         <v>34</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12521,7 +12521,7 @@
         <v>34</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12553,7 +12553,7 @@
         <v>34</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12585,7 +12585,7 @@
         <v>34</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12617,7 +12617,7 @@
         <v>34</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12649,7 +12649,7 @@
         <v>34</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12681,7 +12681,7 @@
         <v>34</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89" ht="31" customHeight="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12713,7 +12713,7 @@
         <v>34</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-11 21:53 UTC</t>
+    <t>2026-10-12 08:40 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -28,7 +28,7 @@
     <t>Verified V1 features</t>
   </si>
   <si>
-    <t>1 / 140</t>
+    <t>2 / 140</t>
   </si>
   <si>
     <t>V1 feature progress</t>
@@ -3100,7 +3100,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>0.007142857142857143</v>
+        <v>0.014285714285714285</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3404,8 +3404,8 @@
       </c>
     </row>
     <row r="10" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>26</v>
+      <c r="A10" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>54</v>
@@ -3426,7 +3426,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>56</v>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -43,7 +43,7 @@
     <t>Last synchronized (UTC)</t>
   </si>
   <si>
-    <t>2026-10-12 08:40 UTC</t>
+    <t>2026-10-17 06:33 UTC</t>
   </si>
   <si>
     <t>Source</t>

--- a/tracking/Project_Checklist.xlsx
+++ b/tracking/Project_Checklist.xlsx
@@ -28,7 +28,7 @@
     <t>Verified V1 features</t>
   </si>
   <si>
-    <t>2 / 140</t>
+    <t>3 / 140</t>
   </si>
   <si>
     <t>V1 feature progress</t>
@@ -3100,7 +3100,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>0.014285714285714285</v>
+        <v>0.02142857142857143</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3439,8 +3439,8 @@
       </c>
     </row>
     <row r="11" ht="31" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>26</v>
+      <c r="A11" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>58</v>
@@ -3461,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>60</v>
